--- a/output/pdf_financials_xlsx/XCAP.P.xlsx
+++ b/output/pdf_financials_xlsx/XCAP.P.xlsx
@@ -3390,25 +3390,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.101185</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.09871199999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.102267</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.102267</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.102267</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.102267</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.102267</v>
       </c>
     </row>
     <row r="93">
@@ -5158,7 +5158,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -5648,7 +5652,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -5756,7 +5764,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XCAP.P.xlsx
+++ b/output/pdf_financials_xlsx/XCAP.P.xlsx
@@ -762,25 +762,25 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011239</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00359</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002399</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.023104</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.049179</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.041425</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.021798</v>
       </c>
     </row>
     <row r="13">
@@ -1271,25 +1271,25 @@
         <v>-0.049898</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.180976</v>
+        <v>-0.192215</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.103904</v>
+        <v>-0.107494</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.085129</v>
+        <v>-0.08752799999999999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.051365</v>
+        <v>-0.07446899999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.04186</v>
+        <v>-0.09103899999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.045084</v>
+        <v>-0.086509</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.139832</v>
+        <v>-0.16163</v>
       </c>
     </row>
     <row r="28">
@@ -1333,25 +1333,25 @@
         <v>-0.049898</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.180976</v>
+        <v>-0.192215</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.103904</v>
+        <v>-0.107494</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.085129</v>
+        <v>-0.08752799999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.051365</v>
+        <v>-0.07446899999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.04186</v>
+        <v>-0.09103899999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.045084</v>
+        <v>-0.086509</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.139832</v>
+        <v>-0.16163</v>
       </c>
     </row>
     <row r="30">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
